--- a/10_Threshold_OUTPUT/reverse_P0A9Q1_Escherichia_coli_str__K-12_substr__MG1655.xlsx
+++ b/10_Threshold_OUTPUT/reverse_P0A9Q1_Escherichia_coli_str__K-12_substr__MG1655.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TTGTTAAAAAAATGTTAAAA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TTGTTA</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>TTAAAA</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;AAAAAATG&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.02678928428628548</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>TTGTTAAAA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TTGT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>AAAA</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;T&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.81187524990004</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>AAAAAAAT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>AAAA</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>AAAT</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.9986005597760895</v>
       </c>
     </row>
@@ -564,15 +604,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>TTAAAAAAATGTTAA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>TTAA</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>TTAA</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;AAAAATG&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.195921631347461</v>
       </c>
     </row>
@@ -593,15 +643,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>TTAAAAA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>TTA</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;A&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -622,15 +682,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>AAAAAAT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>AAT</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;A&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -651,15 +721,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>TGTTAAA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>TGT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;T&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.9964014394242303</v>
       </c>
     </row>
@@ -680,15 +760,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTGTTA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>TA</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;GT&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -709,15 +799,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTGTTAA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;GTT&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -738,15 +838,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTAA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.9936025589764095</v>
       </c>
     </row>
@@ -767,15 +877,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTGTTAAA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;GTTA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -796,15 +916,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTAAA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;A&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -825,15 +955,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTAAAA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;AA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -854,15 +994,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTGTTAAAAA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;GTTAAA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -883,15 +1033,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTGTTAAAAAA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;GTTAAAA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -912,15 +1072,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTAAAAAA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;AAAA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -941,15 +1111,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTGTTAAAAAAA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;GTTAAAAA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -970,15 +1150,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTAAAAAAA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;AAAAA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -999,15 +1189,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>TAAAAAAA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>TA</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;AAAA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1028,15 +1228,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTGTTAAAAAAAT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;GTTAAAAAA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1057,15 +1267,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAAAT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;A&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1086,15 +1306,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAAT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1115,15 +1345,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAAAAATGTT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;AAAATG&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1144,15 +1384,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAAAATGTT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;AAATG&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1173,15 +1423,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAATGTT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;ATG&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1202,15 +1462,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AATGTT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;TG&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1231,15 +1501,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AATGTTA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>TA</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;TGT&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1260,15 +1540,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTGTTAAAAAAATGTTAA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;GTTAAAAAAATGTT&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1289,15 +1579,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>ATGTTAA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;GTT&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1318,15 +1618,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTAA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1347,15 +1657,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTAAAAAAATGTTAAA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;AAAAAAATGTTA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1376,15 +1696,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTAAA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;A&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1405,15 +1735,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTAAAAAAATGTTAAAA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;AAAAAAATGTTAA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1434,15 +1774,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTAAAA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;AA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1463,15 +1813,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTGTTAAAAAAATGTTAAAAA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;GTTAAAAAAATGTTAAA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1492,15 +1852,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTAAAAAAATGTTAAAAA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;AAAAAAATGTTAAA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1521,15 +1891,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTAAAAA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;AAA&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>

--- a/10_Threshold_OUTPUT/reverse_P0A9Q1_Escherichia_coli_str__K-12_substr__MG1655.xlsx
+++ b/10_Threshold_OUTPUT/reverse_P0A9Q1_Escherichia_coli_str__K-12_substr__MG1655.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>p_value</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -508,6 +513,11 @@
       <c r="I2" t="n">
         <v>0.02678928428628548</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -547,6 +557,11 @@
       <c r="I3" t="n">
         <v>0.81187524990004</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -585,6 +600,11 @@
       </c>
       <c r="I4" t="n">
         <v>0.9986005597760895</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -625,6 +645,11 @@
       <c r="I5" t="n">
         <v>0.195921631347461</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -664,6 +689,11 @@
       <c r="I6" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -703,6 +733,11 @@
       <c r="I7" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -742,6 +777,11 @@
       <c r="I8" t="n">
         <v>0.9964014394242303</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -781,6 +821,11 @@
       <c r="I9" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -820,6 +865,11 @@
       <c r="I10" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -859,6 +909,11 @@
       <c r="I11" t="n">
         <v>0.9936025589764095</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -898,6 +953,11 @@
       <c r="I12" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -937,6 +997,11 @@
       <c r="I13" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -976,6 +1041,11 @@
       <c r="I14" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1015,6 +1085,11 @@
       <c r="I15" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1054,6 +1129,11 @@
       <c r="I16" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1093,6 +1173,11 @@
       <c r="I17" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1132,6 +1217,11 @@
       <c r="I18" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1171,6 +1261,11 @@
       <c r="I19" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1210,6 +1305,11 @@
       <c r="I20" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1249,6 +1349,11 @@
       <c r="I21" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1288,6 +1393,11 @@
       <c r="I22" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1327,6 +1437,11 @@
       <c r="I23" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1366,6 +1481,11 @@
       <c r="I24" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1405,6 +1525,11 @@
       <c r="I25" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1444,6 +1569,11 @@
       <c r="I26" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1483,6 +1613,11 @@
       <c r="I27" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -1522,6 +1657,11 @@
       <c r="I28" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -1561,6 +1701,11 @@
       <c r="I29" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1600,6 +1745,11 @@
       <c r="I30" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -1639,6 +1789,11 @@
       <c r="I31" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1678,6 +1833,11 @@
       <c r="I32" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1717,6 +1877,11 @@
       <c r="I33" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -1756,6 +1921,11 @@
       <c r="I34" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1795,6 +1965,11 @@
       <c r="I35" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1834,6 +2009,11 @@
       <c r="I36" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1873,6 +2053,11 @@
       <c r="I37" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1911,6 +2096,11 @@
       </c>
       <c r="I38" t="n">
         <v>0.9998000799680128</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/10_Threshold_OUTPUT/reverse_P0A9Q1_Escherichia_coli_str__K-12_substr__MG1655.xlsx
+++ b/10_Threshold_OUTPUT/reverse_P0A9Q1_Escherichia_coli_str__K-12_substr__MG1655.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>evaluation</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>correctness_%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -518,6 +523,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>66.67</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -562,6 +570,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K3" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -605,6 +616,9 @@
         <is>
           <t>Ambiguous IR</t>
         </is>
+      </c>
+      <c r="K4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -650,6 +664,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -694,6 +711,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K6" t="n">
+        <v>66.67</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -738,6 +758,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K7" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -782,6 +805,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K8" t="n">
+        <v>66.67</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -826,6 +852,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K9" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -870,6 +899,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -914,6 +946,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -958,6 +993,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1002,6 +1040,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1046,6 +1087,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1090,6 +1134,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K15" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1134,6 +1181,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1178,6 +1228,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K17" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1222,6 +1275,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1266,6 +1322,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K19" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1310,6 +1369,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K20" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1354,6 +1416,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K21" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1398,6 +1463,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K22" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1442,6 +1510,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K23" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1486,6 +1557,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K24" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1530,6 +1604,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K25" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1574,6 +1651,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K26" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1618,6 +1698,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K27" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -1662,6 +1745,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K28" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -1706,6 +1792,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K29" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1750,6 +1839,9 @@
           <t>Ambiguous IR</t>
         </is>
       </c>
+      <c r="K30" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -1794,6 +1886,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K31" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1838,6 +1933,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K32" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1882,6 +1980,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K33" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -1926,6 +2027,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K34" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1970,6 +2074,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K35" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2014,6 +2121,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K36" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2058,6 +2168,9 @@
           <t>Confirmed IR</t>
         </is>
       </c>
+      <c r="K37" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -2101,6 +2214,9 @@
         <is>
           <t>Confirmed IR</t>
         </is>
+      </c>
+      <c r="K38" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
